--- a/Topics2.xlsx
+++ b/Topics2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be3e99465cf27169/Admin/WebApps/MathsDatabase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{8BF0E0B7-FF5C-4A2F-975E-807AD203F207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E469EF6-BF80-48C9-BDBD-B161BE8AF453}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{8BF0E0B7-FF5C-4A2F-975E-807AD203F207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9013E7B-99A2-4A1C-9652-7D61F5DBD661}"/>
   <bookViews>
     <workbookView xWindow="10320" yWindow="2880" windowWidth="30960" windowHeight="12660" xr2:uid="{5F3515D1-ED24-4918-92E0-EFD994F45BDC}"/>
   </bookViews>
@@ -36,39 +36,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
-  <si>
-    <t>Linear Relationships</t>
-  </si>
-  <si>
-    <t>Measurement</t>
-  </si>
-  <si>
-    <t>Financial Maths</t>
-  </si>
-  <si>
-    <t>Networks</t>
-  </si>
-  <si>
-    <t>Flow</t>
-  </si>
-  <si>
-    <t>Critical Path</t>
-  </si>
-  <si>
-    <t>Depreciation straight-line</t>
-  </si>
-  <si>
-    <t>Shares</t>
-  </si>
-  <si>
-    <t>Linear Modelling</t>
-  </si>
-  <si>
-    <t>Concepts and Trees</t>
-  </si>
-  <si>
-    <t>Trapezoidal Rule</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Subtopic</t>
+  </si>
+  <si>
+    <t>Polynomials</t>
+  </si>
+  <si>
+    <t>Vectors</t>
+  </si>
+  <si>
+    <t>Inverse functions</t>
+  </si>
+  <si>
+    <t>Related rates of change</t>
+  </si>
+  <si>
+    <t>Further Calculus</t>
+  </si>
+  <si>
+    <t>Exponential growth and decay</t>
+  </si>
+  <si>
+    <t>Solids of revolution</t>
+  </si>
+  <si>
+    <t>Differential equations</t>
+  </si>
+  <si>
+    <t>Differentiating inverse trig</t>
+  </si>
+  <si>
+    <t>Integrating inverse trig</t>
+  </si>
+  <si>
+    <t>Integration by substitution</t>
+  </si>
+  <si>
+    <t>Integrating sin² and cos²</t>
+  </si>
+  <si>
+    <t>Further Trigonometry</t>
+  </si>
+  <si>
+    <t>Compound angle identities</t>
+  </si>
+  <si>
+    <t>Solving equations using identities</t>
+  </si>
+  <si>
+    <t>Auxiliary angle formula</t>
+  </si>
+  <si>
+    <t>t Formula</t>
+  </si>
+  <si>
+    <t>Further Functions</t>
+  </si>
+  <si>
+    <t>Further transformations</t>
+  </si>
+  <si>
+    <t>Parametric form</t>
+  </si>
+  <si>
+    <t>Rational and absolute value inequalities</t>
+  </si>
+  <si>
+    <t>Dot product</t>
+  </si>
+  <si>
+    <t>Projection</t>
+  </si>
+  <si>
+    <t>Mechanics applications</t>
+  </si>
+  <si>
+    <t>Projectile motion</t>
+  </si>
+  <si>
+    <t>Inverse trigonometric functions</t>
+  </si>
+  <si>
+    <t>Combinatorics</t>
+  </si>
+  <si>
+    <t>Permutations and combinations</t>
+  </si>
+  <si>
+    <t>Binomial theorem</t>
+  </si>
+  <si>
+    <t>Sum and product of roots</t>
+  </si>
+  <si>
+    <t>Proof</t>
+  </si>
+  <si>
+    <t>Induction</t>
+  </si>
+  <si>
+    <t>Binomial distributions</t>
+  </si>
+  <si>
+    <t>Sample means</t>
   </si>
 </sst>
 </file>
@@ -440,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC17005-3F68-4D76-AB6F-A3AD581A36F2}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
@@ -449,15 +524,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -465,42 +540,204 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
